--- a/output/pdf_financials_xlsx/TA.xlsx
+++ b/output/pdf_financials_xlsx/TA.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/TA.xlsx
+++ b/output/pdf_financials_xlsx/TA.xlsx
@@ -452,12 +452,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12</t>
         </is>
       </c>
     </row>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2569</v>
+        <v>756</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1830</v>
+        <v>613</v>
       </c>
     </row>
     <row r="76">
@@ -2315,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2364,24 +2364,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" s="5" t="n">
-        <v>337</v>
+        <v>2026</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>205</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2397,19 +2393,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted cash (Note 25)</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RestrictedCash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>69</v>
+        <v>337</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>78</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4">
@@ -2425,19 +2421,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trade and other receivables (Note 13)</t>
+          <t>Restricted cash (Note 25)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AccountsReceivable</t>
+          <t>RestrictedCash</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>767</v>
+        <v>69</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>699</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
@@ -2453,19 +2449,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prepaid expenses and other</t>
+          <t>Trade and other receivables (Note 13)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>68</v>
+        <v>767</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>51</v>
+        <v>699</v>
       </c>
     </row>
     <row r="6">
@@ -2481,15 +2477,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk management assets (Note 14 and 15)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Prepaid expenses and other</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="n">
-        <v>318</v>
+        <v>68</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>162</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -2505,19 +2505,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inventory (Note 16)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
+          <t>Risk management assets (Note 14 and 15)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" s="5" t="n">
-        <v>134</v>
+        <v>318</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
@@ -2533,19 +2529,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assets held for sale (Note 4 and 18)</t>
+          <t>Inventory (Note 16)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AssetsHeldForSale</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>30</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9">
@@ -2561,19 +2557,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Current assets total</t>
+          <t>Assets held for sale (Note 4 and 18)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>AssetsHeldForSale</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1773</v>
+        <v>80</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1336</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -2584,24 +2580,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Investments (Note 9)</t>
+          <t>Current assets total</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>InvestmentsAndAdvances</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>159</v>
+        <v>1773</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>144</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="11">
@@ -2617,15 +2613,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Long-term portion of finance lease receivables (Note 17)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Investments (Note 9)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
-        <v>305</v>
+        <v>159</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>277</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
@@ -2641,15 +2641,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk management assets (Note 14 and 15)</t>
+          <t>Long-term portion of finance lease receivables (Note 17)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="5" t="n">
-        <v>93</v>
+        <v>305</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>32</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13">
@@ -2665,19 +2665,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Property, plant and equipment (Note 19)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NetPPE</t>
-        </is>
-      </c>
+          <t>Risk management assets (Note 14 and 15)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" s="5" t="n">
-        <v>6020</v>
+        <v>93</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>5665</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -2693,7 +2689,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Right-of-use assets (Note 20)</t>
+          <t>Property, plant and equipment (Note 19)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2702,10 +2698,10 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>120</v>
+        <v>6020</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>111</v>
+        <v>5665</v>
       </c>
     </row>
     <row r="15">
@@ -2721,19 +2717,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Intangible assets (Note 21)</t>
+          <t>Right-of-use assets (Note 20)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>281</v>
+        <v>120</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>243</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -2749,19 +2745,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Goodwill (Note 22)</t>
+          <t>Intangible assets (Note 21)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>OtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>517</v>
+        <v>281</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>516</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17">
@@ -2777,15 +2773,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deferred income tax assets (Note 11)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Goodwill (Note 22)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
-        <v>52</v>
+        <v>517</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>41</v>
+        <v>516</v>
       </c>
     </row>
     <row r="18">
@@ -2801,21 +2801,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long-term financial assets (Note 14)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FinancialAssets</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred income tax assets (Note 11)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>52</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>140</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -2831,19 +2825,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other assets (Note 23)</t>
+          <t>Long-term financial assets (Note 14)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OtherAssets</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>179</v>
+          <t>FinancialAssets</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -2859,19 +2855,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Other assets (Note 23)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
+          <t>OtherAssets</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>9499</v>
+        <v>179</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>8661</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21">
@@ -2882,22 +2878,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bank overdraft</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9499</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>8661</v>
       </c>
     </row>
     <row r="22">
@@ -2913,19 +2911,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Accounts payable, accrued liabilities and other current liabilities (Note 13)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CurrentLiabilities</t>
-        </is>
-      </c>
+          <t>Bank overdraft</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" s="5" t="n">
-        <v>756</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>613</v>
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2941,15 +2937,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Current portion of decommissioning and other provisions (Note 24)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Accounts payable, accrued liabilities and other current liabilities (Note 13)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OtherCurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>83</v>
+        <v>756</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>84</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24">
@@ -2965,15 +2965,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Risk management liabilities (Note 14 and 15)</t>
+          <t>Current portion of decommissioning and other provisions (Note 24)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="5" t="n">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>156</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -2989,19 +2989,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dividends payable (Note 28 and 29)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>DividendsPayable</t>
-        </is>
-      </c>
+          <t>Risk management liabilities (Note 14 and 15)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>49</v>
+        <v>277</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>52</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
@@ -3017,15 +3013,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Exchangeable securities (Note 26)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Dividends payable (Note 28 and 29)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DividendsPayable</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>750</v>
+        <v>49</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>750</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
@@ -3041,17 +3041,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contingent consideration payable (Note 4 and 7)</t>
+          <t>Exchangeable securities (Note 26)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>750</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="28">
@@ -3067,15 +3065,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Current portion of long-term debt and lease liabilities (Note 25)</t>
+          <t>Contingent consideration payable (Note 4 and 7)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>572</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>175</v>
+        <v>81</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -3091,19 +3091,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Current liabilities total</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CurrentLiabilities</t>
-        </is>
-      </c>
+          <t>Current portion of long-term debt and lease liabilities (Note 25)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>2569</v>
+        <v>572</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>1830</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30">
@@ -3114,20 +3110,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Credit facilities, long-term debt and lease liabilities (Note 25)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Current liabilities total</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
-        <v>3236</v>
+        <v>2569</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>3418</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="31">
@@ -3143,15 +3143,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Decommissioning and other provisions (Note 24)</t>
+          <t>Credit facilities, long-term debt and lease liabilities (Note 25)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>850</v>
+        <v>3236</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>807</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="32">
@@ -3167,15 +3167,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Deferred income tax liabilities (Note 11)</t>
+          <t>Decommissioning and other provisions (Note 24)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="5" t="n">
-        <v>470</v>
+        <v>850</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>423</v>
+        <v>807</v>
       </c>
     </row>
     <row r="33">
@@ -3191,15 +3191,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Risk management liabilities (Note 14 and 15)</t>
+          <t>Deferred income tax liabilities (Note 11)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>305</v>
+        <v>470</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>519</v>
+        <v>423</v>
       </c>
     </row>
     <row r="34">
@@ -3215,15 +3215,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Contract liabilities (Note 5)</t>
+          <t>Risk management liabilities (Note 14 and 15)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>24</v>
+        <v>305</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>26</v>
+        <v>519</v>
       </c>
     </row>
     <row r="35">
@@ -3239,15 +3239,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Defined benefit obligation and other long-term liabilities (Note 27)</t>
+          <t>Contract liabilities (Note 5)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="n">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>173</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36">
@@ -3263,19 +3263,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
+          <t>Defined benefit obligation and other long-term liabilities (Note 27)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" s="5" t="n">
-        <v>7656</v>
+        <v>202</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>7196</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37">
@@ -3284,22 +3280,26 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Non-current liabilities</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Common shares (Note 28)</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CommonStock</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>3179</v>
+        <v>7656</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>3169</v>
+        <v>7196</v>
       </c>
     </row>
     <row r="38">
@@ -3311,19 +3311,19 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Preferred shares (Note 29)</t>
+          <t>Common shares (Note 28)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PreferredStock</t>
+          <t>CommonStock</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>942</v>
+        <v>3179</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>942</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="39">
@@ -3335,19 +3335,19 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Preferred shares (Note 29)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
+          <t>PreferredStock</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>42</v>
+        <v>942</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>42</v>
+        <v>942</v>
       </c>
     </row>
     <row r="40">
@@ -3359,19 +3359,19 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-2458</v>
+        <v>42</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-2730</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -3383,19 +3383,19 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Accumulated other comprehensive (loss) income (Note 30)</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GainsLossesNotAffectingRetainedEarnings</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>41</v>
+        <v>-2458</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-24</v>
+        <v>-2730</v>
       </c>
     </row>
     <row r="42">
@@ -3407,19 +3407,19 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders</t>
+          <t>Accumulated other comprehensive (loss) income (Note 30)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1746</v>
+        <v>41</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>1399</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="43">
@@ -3431,19 +3431,19 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Non-controlling interests (Note 12)</t>
+          <t>Equity attributable to shareholders</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MinorityInterest</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>97</v>
+        <v>1746</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>66</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44">
@@ -3455,19 +3455,19 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Total equity</t>
+          <t>Non-controlling interests (Note 12)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TotalEquityGrossMinorityInterest</t>
+          <t>MinorityInterest</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1843</v>
+        <v>97</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>1465</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45">
@@ -3479,43 +3479,43 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Total liabilities and equity</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>TotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>9499</v>
+        <v>1843</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>8661</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Net (loss) income</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
-        <v>239</v>
+        <v>9499</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-158</v>
+        <v>8661</v>
       </c>
     </row>
     <row r="47">
@@ -3531,19 +3531,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Depreciation and amortization (Note 19, 20, 21 and 27)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Net (loss) income</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>531</v>
+        <v>239</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>579</v>
+        <v>-158</v>
       </c>
     </row>
     <row r="48">
@@ -3559,15 +3555,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gain on sale of assets and other</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Depreciation and amortization (Note 19, 20, 21 and 27)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
-        <v>-1</v>
+        <v>531</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-1</v>
+        <v>579</v>
       </c>
     </row>
     <row r="49">
@@ -3583,15 +3583,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Accretion of provisions (Note 10 and 24)</t>
+          <t>Gain on sale of assets and other</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>50</v>
+        <v>-1</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>57</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50">
@@ -3607,15 +3607,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Decommissioning and restoration costs settled (Note 24)</t>
+          <t>Accretion of provisions (Note 10 and 24)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>-41</v>
+        <v>50</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51">
@@ -3631,15 +3631,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (Note 11)</t>
+          <t>Decommissioning and restoration costs settled (Note 24)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>-63</v>
+        <v>-41</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-32</v>
+        <v>-39</v>
       </c>
     </row>
     <row r="52">
@@ -3655,15 +3655,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Unrealized loss from risk management activities</t>
+          <t>Deferred income tax recovery (Note 11)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>-63</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>289</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="53">
@@ -3679,15 +3679,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange loss (gain)</t>
+          <t>Unrealized loss from risk management activities</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>-29</v>
+        <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>6</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54">
@@ -3703,15 +3703,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Provisions and contract liabilities</t>
+          <t>Unrealized foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>23</v>
+        <v>-29</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -3727,15 +3727,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Asset impairment (reversals) charges (Note 7)</t>
+          <t>Provisions and contract liabilities</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-13</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="56">
@@ -3751,17 +3751,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Equity income, net of distributions from investments (Note 9)</t>
+          <t>Asset impairment (reversals) charges (Note 7)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="5" t="n">
+        <v>46</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-1</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="57">
@@ -3777,19 +3775,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Other non-cash items</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>OtherNonCashItems</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>1</v>
+          <t>Equity income, net of distributions from investments (Note 9)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58">
@@ -3805,15 +3801,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cash flow from operations before changes in working capital</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Other non-cash items</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
-        <v>758</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>643</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="59">
@@ -3829,15 +3829,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Change in non-cash operating working capital balances (Note 33)</t>
+          <t>Cash flow from operations before changes in working capital</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>38</v>
+        <v>758</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>3</v>
+        <v>643</v>
       </c>
     </row>
     <row r="60">
@@ -3853,19 +3853,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash flow from operating activities</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Change in non-cash operating working capital balances (Note 33)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>796</v>
+        <v>38</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>646</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3876,24 +3872,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Additions to property, plant and equipment (Note 19 and 37)</t>
+          <t>Cash flow from operating activities</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PurchaseOfPPE</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>-311</v>
+        <v>796</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-249</v>
+        <v>646</v>
       </c>
     </row>
     <row r="62">
@@ -3909,15 +3905,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Additions to intangible assets (Note 21 and 37)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Additions to property, plant and equipment (Note 19 and 37)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
-        <v>-10</v>
+        <v>-311</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-11</v>
+        <v>-249</v>
       </c>
     </row>
     <row r="63">
@@ -3933,15 +3933,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Restricted cash (Note 25)</t>
+          <t>Additions to intangible assets (Note 21 and 37)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="64">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Loan advances (Note 23)</t>
+          <t>Restricted cash (Note 25)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -3965,7 +3965,7 @@
         <v>-1</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="65">
@@ -3981,17 +3981,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Acquisitions, net of cash acquired (Note 4)</t>
+          <t>Loan advances (Note 23)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>-217</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="66">
@@ -4007,17 +4005,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Increase in long-term financial assets (Note 14)</t>
+          <t>Acquisitions, net of cash acquired (Note 4)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>-145</v>
+      <c r="E66" s="5" t="n">
+        <v>-217</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4033,15 +4031,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Investments (Note 9)</t>
+          <t>Increase in long-term financial assets (Note 14)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>-5</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-7</v>
+        <v>-145</v>
       </c>
     </row>
     <row r="68">
@@ -4057,15 +4057,15 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Proceeds on sale of property, plant and equipment</t>
+          <t>Investments (Note 9)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="69">
@@ -4081,15 +4081,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Realized (loss) gain on financial instruments</t>
+          <t>Proceeds on sale of property, plant and equipment</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -4105,15 +4105,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Decrease in finance lease receivable (Note 17)</t>
+          <t>Realized (loss) gain on financial instruments</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>30</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="71">
@@ -4129,15 +4129,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Development expenditures</t>
+          <t>Decrease in finance lease receivable (Note 17)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>-6</v>
+        <v>21</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72">
@@ -4153,15 +4153,15 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Development expenditures</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" s="5" t="n">
-        <v>25</v>
+        <v>-6</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="73">
@@ -4177,15 +4177,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Change in non-cash investing working capital balances</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" s="5" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-23</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="74">
@@ -4201,19 +4201,15 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cash flow used in investing activities</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Change in non-cash investing working capital balances</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="n">
-        <v>-520</v>
+        <v>-20</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-418</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="75">
@@ -4224,20 +4220,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Net (decrease) increase in borrowings under credit facilities (Note 25 and 33)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Cash flow used in investing activities</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
-        <v>143</v>
+        <v>-520</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-448</v>
+        <v>-418</v>
       </c>
     </row>
     <row r="76">
@@ -4253,19 +4253,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Repayment of long-term debt (Note 25 and 33)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>RepaymentOfDebt</t>
-        </is>
-      </c>
+          <t>Net (decrease) increase in borrowings under credit facilities (Note 25 and 33)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" s="5" t="n">
-        <v>-131</v>
+        <v>143</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-736</v>
+        <v>-448</v>
       </c>
     </row>
     <row r="77">
@@ -4281,17 +4277,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Issuance of long-term debt (Note 25 and 33)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Repayment of long-term debt (Note 25 and 33)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-131</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>991</v>
+        <v>-736</v>
       </c>
     </row>
     <row r="78">
@@ -4307,15 +4305,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dividends paid on common shares (Note 28)</t>
+          <t>Issuance of long-term debt (Note 25 and 33)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>-71</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-74</v>
+        <v>991</v>
       </c>
     </row>
     <row r="79">
@@ -4331,15 +4331,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dividends paid on preferred shares (Note 29)</t>
+          <t>Dividends paid on common shares (Note 28)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>-52</v>
+        <v>-71</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-52</v>
+        <v>-74</v>
       </c>
     </row>
     <row r="80">
@@ -4355,15 +4355,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Repurchase of common shares under NCIB (Note 28)</t>
+          <t>Dividends paid on preferred shares (Note 29)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>-143</v>
+        <v>-52</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-24</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="81">
@@ -4379,19 +4379,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Proceeds on issuance of common shares</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
+          <t>Repurchase of common shares under NCIB (Note 28)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>12</v>
+        <v>-143</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>3</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="82">
@@ -4407,15 +4403,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Realized gain on financial instruments</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Proceeds on issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -4431,15 +4431,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Distributions paid to subsidiaries' non-controlling interests (Note 12)</t>
+          <t>Realized gain on financial instruments</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" s="5" t="n">
-        <v>-40</v>
+        <v>4</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -4455,15 +4455,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Decrease in lease liabilities (Note 25 and 33)</t>
+          <t>Distributions paid to subsidiaries' non-controlling interests (Note 12)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="5" t="n">
-        <v>-6</v>
+        <v>-40</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="85">
@@ -4479,15 +4479,15 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Financing fees and other</t>
+          <t>Decrease in lease liabilities (Note 25 and 33)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="86">
@@ -4503,15 +4503,15 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Change in non-cash financing working capital balances</t>
+          <t>Financing fees and other</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="87">
@@ -4527,19 +4527,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cash flow used in financing activities</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Change in non-cash financing working capital balances</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" s="5" t="n">
-        <v>-291</v>
+        <v>-6</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-362</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88">
@@ -4555,15 +4551,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cash flow used in operating, investing and financing activities</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Cash flow used in financing activities</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
-        <v>-15</v>
+        <v>-291</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-134</v>
+        <v>-362</v>
       </c>
     </row>
     <row r="89">
@@ -4579,15 +4579,15 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Effect of translation on foreign currency cash</t>
+          <t>Cash flow used in operating, investing and financing activities</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>-15</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>2</v>
+        <v>-134</v>
       </c>
     </row>
     <row r="90">
@@ -4603,19 +4603,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Decrease in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Effect of translation on foreign currency cash</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" s="5" t="n">
-        <v>-11</v>
+        <v>4</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-132</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -4631,19 +4627,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Decrease in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>348</v>
+        <v>-11</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>337</v>
+        <v>-132</v>
       </c>
     </row>
     <row r="92">
@@ -4659,19 +4655,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
+        <v>348</v>
+      </c>
+      <c r="F92" s="5" t="n">
         <v>337</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>205</v>
       </c>
     </row>
     <row r="93">
@@ -4687,15 +4683,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cash taxes paid</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
-        <v>104</v>
+        <v>337</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>85</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94">
@@ -4711,15 +4711,15 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cash interest paid</t>
+          <t>Cash taxes paid</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" s="5" t="n">
-        <v>269</v>
+        <v>104</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>282</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95">
@@ -4735,14 +4735,42 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>Cash interest paid</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>Cash interest received</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="F95" s="5" t="n">
+      <c r="F96" s="5" t="n">
         <v>28</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/TA.xlsx
+++ b/output/pdf_financials_xlsx/TA.xlsx
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>756</v>
+        <v>2569</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>613</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="76">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">

--- a/output/pdf_financials_xlsx/TA.xlsx
+++ b/output/pdf_financials_xlsx/TA.xlsx
@@ -3936,7 +3936,11 @@
           <t>Additions to intangible assets (Note 21 and 37)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>-10</v>
       </c>

--- a/output/pdf_financials_xlsx/TA.xlsx
+++ b/output/pdf_financials_xlsx/TA.xlsx
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>548</v>
       </c>
     </row>
     <row r="65">
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>548</v>
       </c>
     </row>
     <row r="69">
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2569</v>
+        <v>1875</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1830</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="76">
@@ -3658,7 +3658,11 @@
           <t>Deferred income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>-63</v>
       </c>
